--- a/呉俊鋒_週報_2025年6月分.xlsx
+++ b/呉俊鋒_週報_2025年6月分.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DEFF15-C543-4B0D-8208-A6B7E01BA92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B957E998-FDCB-4B8F-8471-7109B47779C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年6月2日の週" sheetId="6" r:id="rId1"/>
+    <sheet name="2025年6月9日の週" sheetId="8" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="Holiday">[1]祝日!$A$2:$B$335</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2025年6月2日の週'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2025年6月9日の週'!$A$1:$K$20</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -32,14 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
-  <si>
-    <t>名前</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>所属</t>
     <rPh sb="0" eb="2">
@@ -168,6 +163,84 @@
   </si>
   <si>
     <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今週の進捗状況：TypeScript勉強
+来週の進捗予定：</t>
+    <rPh sb="18" eb="20">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・6/9
+　■Angularの勉強資料は少ないため、勉強し続いたら、つらいです。</t>
+    <rPh sb="15" eb="17">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・6/9
+　■Angularの勉強資料は少ないため、勉強し続いたら、つらいです。
+　　AngularやVueなどのJSはTypeScriptによって開発したフロントエンドフレームワークため、直接にTypeScriptを
+　　勉強しましょう。あとはAngularの特徴を再び勉強する。</t>
+    <rPh sb="74" eb="76">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="134" eb="135">
+      <t>フタタ</t>
+    </rPh>
+    <rPh sb="136" eb="138">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・6/9
+　プロジェットソース例を作成した。
+・6/10~6/12
+　TypeScriptを勉強した。
+・6/13
+　AWS Cloud Practitioner勉強着手した。</t>
+    <rPh sb="15" eb="16">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>チャクシュ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3602,34 +3675,34 @@
   <sheetData>
     <row r="1" spans="2:13" s="2" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B1" s="7" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" s="25"/>
       <c r="E1" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
       <c r="J1" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="2:13" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -3642,10 +3715,10 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B3" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -3721,10 +3794,10 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B9" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -3797,10 +3870,10 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B15" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
@@ -3887,4 +3960,308 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2BE72C-17B7-448C-A193-EC7720C56ADC}">
+  <dimension ref="B1:M20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="7.8984375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="16.3984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.09765625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" s="2" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="25"/>
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B4" s="13"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B5" s="13"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="20"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B6" s="13"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B7" s="13"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" spans="2:13" ht="364.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="30"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B10" s="13"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B12" s="13"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B13" s="13"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="2:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="26"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="30"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B15" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B16" s="13"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B17" s="13"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B18" s="13"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B19" s="13"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="2:11" ht="147.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="14"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="C15:K20"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:K8"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:K14"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/呉俊鋒_週報_2025年6月分.xlsx
+++ b/呉俊鋒_週報_2025年6月分.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B957E998-FDCB-4B8F-8471-7109B47779C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F473AB6-3C49-4CCD-A07E-60794AFB618B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年6月2日の週" sheetId="6" r:id="rId1"/>
     <sheet name="2025年6月9日の週" sheetId="8" r:id="rId2"/>
+    <sheet name="2025年6月16日の週" sheetId="9" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="Holiday">[1]祝日!$A$2:$B$335</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2025年6月16日の週'!$A$1:$K$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2025年6月2日の週'!$A$1:$K$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2025年6月9日の週'!$A$1:$K$20</definedName>
   </definedNames>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t>所属</t>
     <rPh sb="0" eb="2">
@@ -170,14 +172,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>今週の進捗状況：TypeScript勉強
-来週の進捗予定：</t>
-    <rPh sb="18" eb="20">
-      <t>ベンキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・6/9
 　■Angularの勉強資料は少ないため、勉強し続いたら、つらいです。</t>
     <rPh sb="15" eb="17">
@@ -241,6 +235,65 @@
     <rPh sb="83" eb="85">
       <t>チャクシュ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今週の進捗状況：TypeScript勉強
+来週の進捗予定：AWS Cloud Practitioner勉強着手</t>
+    <rPh sb="18" eb="20">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・6/16
+　基本なサービスを勉強した。
+　AWSのインターネットインフラを勉強した。
+・6/17
+　DB&amp;Storageの関連サービスを勉強した。
+・6/18
+　コストの関連サービスを勉強した。
+・6/19
+　移行の関連サービスを勉強した。
+・6/20
+　日本語を勉強した。</t>
+    <rPh sb="7" eb="9">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="129" eb="132">
+      <t>ニホンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今週の進捗状況：AWS Cloud Practitioner勉強着手
+来週の進捗予定：日本語を勉強する</t>
+    <rPh sb="30" eb="32">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>チャクシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特になし</t>
+    <rPh sb="0" eb="1">
+      <t>トク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特になし</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4006,7 +4059,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -4022,7 +4075,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -4101,7 +4154,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -4177,7 +4230,311 @@
         <v>4</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B16" s="13"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B17" s="13"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B18" s="13"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B19" s="13"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="2:11" ht="147.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="14"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="C15:K20"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:K8"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:K14"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9E539D-03D7-421A-88FA-0DB467A8CEA9}">
+  <dimension ref="B1:M20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="7.8984375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="16.3984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.09765625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" s="2" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="25"/>
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B4" s="13"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B5" s="13"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="20"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B6" s="13"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B7" s="13"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" spans="2:13" ht="364.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="30"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B10" s="13"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B12" s="13"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B13" s="13"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="2:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="26"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="30"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B15" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
